--- a/templates/문제_업로드_양식.xlsx
+++ b/templates/문제_업로드_양식.xlsx
@@ -540,21 +540,21 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 문제: 문제 본문 텍스트</t>
+          <t xml:space="preserve">   - 문제: 문제 본문 텍스트 (자료 지문이 있으면 문제 앞에 함께 적어주세요)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 선택지1~4: 객관식 보기 4개 (반드시 4개 모두 채워주세요)</t>
+          <t xml:space="preserve">   - 선택지1~5: 객관식 보기 5개 (반드시 5개 모두 채워주세요)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 정답번호: 정답인 선택지 번호 1~4 중 하나 (드롭다운으로 선택)</t>
+          <t xml:space="preserve">   - 정답번호: 정답인 선택지 번호 1~5 중 하나 (드롭다운으로 선택)</t>
         </is>
       </c>
     </row>
@@ -593,18 +593,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -645,10 +646,15 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>정답번호(1~4)</t>
+          <t>선택지5</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>정답번호(1~5)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>제한시간(초, 선택)</t>
         </is>
@@ -690,10 +696,15 @@
           <t>동의보감</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -731,10 +742,15 @@
           <t>간도 참변</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>훈춘 사건</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -746,6 +762,7 @@
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -757,6 +774,7 @@
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -768,6 +786,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -779,6 +798,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -790,6 +810,7 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -801,6 +822,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -812,6 +834,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -823,6 +846,7 @@
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -834,6 +858,7 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -845,6 +870,7 @@
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -856,6 +882,7 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -867,6 +894,7 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -878,6 +906,7 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -889,6 +918,7 @@
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -900,6 +930,7 @@
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -911,6 +942,7 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -922,6 +954,7 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -933,6 +966,7 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -944,6 +978,7 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -955,6 +990,7 @@
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -966,6 +1002,7 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -977,6 +1014,7 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -988,6 +1026,7 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -999,6 +1038,7 @@
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -1010,6 +1050,7 @@
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -1021,6 +1062,7 @@
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -1032,6 +1074,7 @@
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1043,6 +1086,7 @@
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1054,6 +1098,7 @@
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1065,6 +1110,7 @@
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1076,6 +1122,7 @@
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1087,6 +1134,7 @@
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1098,6 +1146,7 @@
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -1109,6 +1158,7 @@
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -1120,6 +1170,7 @@
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -1131,6 +1182,7 @@
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -1142,6 +1194,7 @@
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -1153,6 +1206,7 @@
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -1164,6 +1218,7 @@
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -1175,6 +1230,7 @@
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -1186,6 +1242,7 @@
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -1197,6 +1254,7 @@
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -1208,6 +1266,7 @@
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -1219,6 +1278,7 @@
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -1230,6 +1290,7 @@
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
       <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -1241,6 +1302,7 @@
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -1252,6 +1314,7 @@
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -1263,6 +1326,7 @@
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
       <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -1274,6 +1338,7 @@
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -1285,6 +1350,7 @@
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
       <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -1296,6 +1362,7 @@
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
       <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -1307,6 +1374,7 @@
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
       <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -1318,6 +1386,7 @@
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -1329,6 +1398,7 @@
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
       <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -1340,6 +1410,7 @@
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -1351,6 +1422,7 @@
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -1362,6 +1434,7 @@
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -1373,6 +1446,7 @@
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
       <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -1384,6 +1458,7 @@
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
       <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -1395,6 +1470,7 @@
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -1406,6 +1482,7 @@
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -1417,6 +1494,7 @@
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
       <c r="I65" s="7" t="n"/>
+      <c r="J65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -1428,6 +1506,7 @@
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
       <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -1439,6 +1518,7 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
+      <c r="J67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -1450,6 +1530,7 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
+      <c r="J68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -1461,6 +1542,7 @@
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
       <c r="I69" s="7" t="n"/>
+      <c r="J69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -1472,6 +1554,7 @@
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
+      <c r="J70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -1483,6 +1566,7 @@
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -1494,6 +1578,7 @@
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="7" t="n"/>
+      <c r="J72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -1505,6 +1590,7 @@
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -1516,6 +1602,7 @@
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="7" t="n"/>
+      <c r="J74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -1527,6 +1614,7 @@
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -1538,6 +1626,7 @@
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
+      <c r="J76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -1549,6 +1638,7 @@
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -1560,6 +1650,7 @@
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
       <c r="I78" s="7" t="n"/>
+      <c r="J78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -1571,6 +1662,7 @@
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
       <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -1582,6 +1674,7 @@
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
       <c r="I80" s="7" t="n"/>
+      <c r="J80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -1593,6 +1686,7 @@
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
       <c r="I81" s="7" t="n"/>
+      <c r="J81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -1604,6 +1698,7 @@
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="7" t="n"/>
+      <c r="J82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -1615,6 +1710,7 @@
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="7" t="n"/>
+      <c r="J83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -1626,6 +1722,7 @@
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="n"/>
       <c r="I84" s="7" t="n"/>
+      <c r="J84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -1637,6 +1734,7 @@
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="7" t="n"/>
+      <c r="J85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -1648,6 +1746,7 @@
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="7" t="n"/>
+      <c r="J86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -1659,6 +1758,7 @@
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -1670,6 +1770,7 @@
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
       <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -1681,6 +1782,7 @@
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="7" t="n"/>
+      <c r="J89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -1692,6 +1794,7 @@
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
       <c r="I90" s="7" t="n"/>
+      <c r="J90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -1703,6 +1806,7 @@
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
       <c r="I91" s="7" t="n"/>
+      <c r="J91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -1714,6 +1818,7 @@
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
+      <c r="J92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -1725,6 +1830,7 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
       <c r="I93" s="7" t="n"/>
+      <c r="J93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -1736,6 +1842,7 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="7" t="n"/>
+      <c r="J94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -1747,6 +1854,7 @@
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="7" t="n"/>
+      <c r="J95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -1758,6 +1866,7 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="7" t="n"/>
+      <c r="J96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -1769,6 +1878,7 @@
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="7" t="n"/>
       <c r="I97" s="7" t="n"/>
+      <c r="J97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -1780,6 +1890,7 @@
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
       <c r="I98" s="7" t="n"/>
+      <c r="J98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -1791,6 +1902,7 @@
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
       <c r="I99" s="7" t="n"/>
+      <c r="J99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -1802,6 +1914,7 @@
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
       <c r="I100" s="7" t="n"/>
+      <c r="J100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -1813,6 +1926,7 @@
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="7" t="n"/>
       <c r="I101" s="7" t="n"/>
+      <c r="J101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -1824,6 +1938,7 @@
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
       <c r="I102" s="7" t="n"/>
+      <c r="J102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -1835,6 +1950,7 @@
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
       <c r="I103" s="7" t="n"/>
+      <c r="J103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -1846,6 +1962,7 @@
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
       <c r="I104" s="7" t="n"/>
+      <c r="J104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -1857,6 +1974,7 @@
       <c r="G105" s="7" t="n"/>
       <c r="H105" s="7" t="n"/>
       <c r="I105" s="7" t="n"/>
+      <c r="J105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -1868,6 +1986,7 @@
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
       <c r="I106" s="7" t="n"/>
+      <c r="J106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -1879,6 +1998,7 @@
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
       <c r="I107" s="7" t="n"/>
+      <c r="J107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -1890,6 +2010,7 @@
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
+      <c r="J108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -1901,6 +2022,7 @@
       <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="n"/>
       <c r="I109" s="7" t="n"/>
+      <c r="J109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -1912,6 +2034,7 @@
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
       <c r="I110" s="7" t="n"/>
+      <c r="J110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -1923,6 +2046,7 @@
       <c r="G111" s="7" t="n"/>
       <c r="H111" s="7" t="n"/>
       <c r="I111" s="7" t="n"/>
+      <c r="J111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -1934,6 +2058,7 @@
       <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="n"/>
       <c r="I112" s="7" t="n"/>
+      <c r="J112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -1945,6 +2070,7 @@
       <c r="G113" s="7" t="n"/>
       <c r="H113" s="7" t="n"/>
       <c r="I113" s="7" t="n"/>
+      <c r="J113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -1956,6 +2082,7 @@
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
       <c r="I114" s="7" t="n"/>
+      <c r="J114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -1967,6 +2094,7 @@
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="n"/>
       <c r="I115" s="7" t="n"/>
+      <c r="J115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -1978,6 +2106,7 @@
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
       <c r="I116" s="7" t="n"/>
+      <c r="J116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -1989,6 +2118,7 @@
       <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="n"/>
       <c r="I117" s="7" t="n"/>
+      <c r="J117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -2000,6 +2130,7 @@
       <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
       <c r="I118" s="7" t="n"/>
+      <c r="J118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -2011,6 +2142,7 @@
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="n"/>
       <c r="I119" s="7" t="n"/>
+      <c r="J119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -2022,6 +2154,7 @@
       <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
       <c r="I120" s="7" t="n"/>
+      <c r="J120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -2033,6 +2166,7 @@
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="n"/>
       <c r="I121" s="7" t="n"/>
+      <c r="J121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -2044,6 +2178,7 @@
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
       <c r="I122" s="7" t="n"/>
+      <c r="J122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -2055,6 +2190,7 @@
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="n"/>
       <c r="I123" s="7" t="n"/>
+      <c r="J123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -2066,6 +2202,7 @@
       <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="n"/>
       <c r="I124" s="7" t="n"/>
+      <c r="J124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -2077,6 +2214,7 @@
       <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="n"/>
       <c r="I125" s="7" t="n"/>
+      <c r="J125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -2088,6 +2226,7 @@
       <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="n"/>
       <c r="I126" s="7" t="n"/>
+      <c r="J126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -2099,6 +2238,7 @@
       <c r="G127" s="7" t="n"/>
       <c r="H127" s="7" t="n"/>
       <c r="I127" s="7" t="n"/>
+      <c r="J127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -2110,6 +2250,7 @@
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
       <c r="I128" s="7" t="n"/>
+      <c r="J128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -2121,6 +2262,7 @@
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="n"/>
       <c r="I129" s="7" t="n"/>
+      <c r="J129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -2132,6 +2274,7 @@
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="n"/>
       <c r="I130" s="7" t="n"/>
+      <c r="J130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -2143,6 +2286,7 @@
       <c r="G131" s="7" t="n"/>
       <c r="H131" s="7" t="n"/>
       <c r="I131" s="7" t="n"/>
+      <c r="J131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -2154,6 +2298,7 @@
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="n"/>
       <c r="I132" s="7" t="n"/>
+      <c r="J132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -2165,6 +2310,7 @@
       <c r="G133" s="7" t="n"/>
       <c r="H133" s="7" t="n"/>
       <c r="I133" s="7" t="n"/>
+      <c r="J133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -2176,6 +2322,7 @@
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
       <c r="I134" s="7" t="n"/>
+      <c r="J134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -2187,6 +2334,7 @@
       <c r="G135" s="7" t="n"/>
       <c r="H135" s="7" t="n"/>
       <c r="I135" s="7" t="n"/>
+      <c r="J135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -2198,6 +2346,7 @@
       <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="n"/>
       <c r="I136" s="7" t="n"/>
+      <c r="J136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -2209,6 +2358,7 @@
       <c r="G137" s="7" t="n"/>
       <c r="H137" s="7" t="n"/>
       <c r="I137" s="7" t="n"/>
+      <c r="J137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -2220,6 +2370,7 @@
       <c r="G138" s="7" t="n"/>
       <c r="H138" s="7" t="n"/>
       <c r="I138" s="7" t="n"/>
+      <c r="J138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -2231,6 +2382,7 @@
       <c r="G139" s="7" t="n"/>
       <c r="H139" s="7" t="n"/>
       <c r="I139" s="7" t="n"/>
+      <c r="J139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -2242,6 +2394,7 @@
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
       <c r="I140" s="7" t="n"/>
+      <c r="J140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -2253,6 +2406,7 @@
       <c r="G141" s="7" t="n"/>
       <c r="H141" s="7" t="n"/>
       <c r="I141" s="7" t="n"/>
+      <c r="J141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -2264,6 +2418,7 @@
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
       <c r="I142" s="7" t="n"/>
+      <c r="J142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -2275,6 +2430,7 @@
       <c r="G143" s="7" t="n"/>
       <c r="H143" s="7" t="n"/>
       <c r="I143" s="7" t="n"/>
+      <c r="J143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -2286,6 +2442,7 @@
       <c r="G144" s="7" t="n"/>
       <c r="H144" s="7" t="n"/>
       <c r="I144" s="7" t="n"/>
+      <c r="J144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -2297,6 +2454,7 @@
       <c r="G145" s="7" t="n"/>
       <c r="H145" s="7" t="n"/>
       <c r="I145" s="7" t="n"/>
+      <c r="J145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -2308,6 +2466,7 @@
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
       <c r="I146" s="7" t="n"/>
+      <c r="J146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -2319,6 +2478,7 @@
       <c r="G147" s="7" t="n"/>
       <c r="H147" s="7" t="n"/>
       <c r="I147" s="7" t="n"/>
+      <c r="J147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -2330,6 +2490,7 @@
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
       <c r="I148" s="7" t="n"/>
+      <c r="J148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -2341,6 +2502,7 @@
       <c r="G149" s="7" t="n"/>
       <c r="H149" s="7" t="n"/>
       <c r="I149" s="7" t="n"/>
+      <c r="J149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -2352,6 +2514,7 @@
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
       <c r="I150" s="7" t="n"/>
+      <c r="J150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -2363,14 +2526,15 @@
       <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="n"/>
       <c r="I151" s="7" t="n"/>
+      <c r="J151" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 난이도" error="하, 중, 고 중 하나를 선택하세요." type="list">
       <formula1>"하,중,고"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 정답번호" error="1, 2, 3, 4 중 하나를 선택하세요." type="list">
-      <formula1>"1,2,3,4"</formula1>
+    <dataValidation sqref="I2:I151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 정답번호" error="1, 2, 3, 4, 5 중 하나를 선택하세요." type="list">
+      <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/문제_업로드_양식.xlsx
+++ b/templates/문제_업로드_양식.xlsx
@@ -561,7 +561,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 제한시간(초): 비워두면 난이도별 기본값 적용(하 15초 / 중 18초 / 고 20초)</t>
+          <t xml:space="preserve">   - 제한시간(초): 비워두면 기본값 60초(1분) 적용</t>
         </is>
       </c>
     </row>
